--- a/doc/6-3#热处理/外法兰.xlsx
+++ b/doc/6-3#热处理/外法兰.xlsx
@@ -110,7 +110,7 @@
     <t>内喷冷却水量</t>
   </si>
   <si>
-    <t>二维码打标内容</t>
+    <t>序列码</t>
   </si>
   <si>
     <t>String</t>

--- a/doc/6-3#热处理/外法兰.xlsx
+++ b/doc/6-3#热处理/外法兰.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="35">
   <si>
     <t>设备名称</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>采集结束</t>
+  </si>
+  <si>
+    <t>能量采集许可</t>
+  </si>
+  <si>
+    <t>能量</t>
+  </si>
+  <si>
+    <t>能量时间</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -1543,6 +1552,91 @@
       </c>
       <c r="J13" s="15"/>
     </row>
+    <row r="14" ht="14.25" spans="1:12">
+      <c r="A14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="6">
+        <v>4990</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="1">
+        <v>524</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="1:12">
+      <c r="A15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="6">
+        <v>4990</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="1">
+        <v>840</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="8">
+        <v>1</v>
+      </c>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" ht="14.25" spans="1:12">
+      <c r="A16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="6">
+        <v>4990</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="1">
+        <v>842</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O13" etc:filterBottomFollowUsedRange="0">
     <extLst/>
@@ -1551,10 +1645,13 @@
     <sortCondition ref="G2"/>
   </sortState>
   <conditionalFormatting sqref="D2">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1 D3:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="E14:E16">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1 D3:D13 D17:D1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/doc/6-3#热处理/外法兰.xlsx
+++ b/doc/6-3#热处理/外法兰.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C2300040802\Desktop\NTP\doc\6-3#热处理\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="19635" windowHeight="7695"/>
   </bookViews>
@@ -10,7 +15,7 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +35,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="38">
+  <si>
+    <t>设备编号</t>
+  </si>
   <si>
     <t>设备名称</t>
   </si>
@@ -41,6 +49,9 @@
     <t>PLC_Port</t>
   </si>
   <si>
+    <t>功能分类</t>
+  </si>
+  <si>
     <t>点位名称</t>
   </si>
   <si>
@@ -63,6 +74,9 @@
   </si>
   <si>
     <t>下发公式</t>
+  </si>
+  <si>
+    <t>6-3#热处理</t>
   </si>
   <si>
     <t>热处理</t>
@@ -1148,25 +1162,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="24.5" customWidth="1"/>
-    <col min="5" max="5" width="8.375" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="7" width="10.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" customWidth="1"/>
-    <col min="9" max="9" width="7.375" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="12.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9" style="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="8.625" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="6" width="24.5" customWidth="1"/>
+    <col min="7" max="7" width="8.375" customWidth="1"/>
+    <col min="8" max="8" width="7.125" customWidth="1"/>
+    <col min="9" max="9" width="10.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" customWidth="1"/>
+    <col min="11" max="11" width="7.375" customWidth="1"/>
+    <col min="12" max="12" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="12.625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:12">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="14.25" spans="1:14">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -1196,461 +1211,527 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="14.25" spans="1:12">
-      <c r="A2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="6">
+    <row r="2" ht="14.25" spans="1:14">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="6">
         <v>4990</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="6">
+        <v>800</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="8">
+        <v>1</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="10"/>
+    </row>
+    <row r="3" ht="14.25" spans="1:14">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="6">
-        <v>800</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="8">
+      <c r="D3" s="6">
+        <v>4990</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="6">
+        <v>801</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="8">
         <v>1</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="10"/>
+      <c r="L3" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" ht="14.25" spans="1:12">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="6">
+    <row r="4" ht="14.25" spans="1:14">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="6">
         <v>4990</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="I4" s="6">
+        <v>802</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="8">
+        <v>1</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6">
-        <v>801</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="8">
+      <c r="D5" s="6">
+        <v>4990</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="6">
+        <v>803</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="8">
         <v>1</v>
       </c>
-      <c r="J3" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="L5" s="9"/>
     </row>
-    <row r="4" ht="14.25" spans="1:12">
-      <c r="A4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="6">
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="6">
         <v>4990</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="6">
+        <v>804</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5" t="s">
+      <c r="K6" s="8">
+        <v>1</v>
+      </c>
+      <c r="L6" s="9"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="6">
-        <v>802</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="8">
+      <c r="D7" s="6">
+        <v>4990</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="6">
+        <v>805</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="8">
         <v>1</v>
       </c>
-      <c r="J4" s="9" t="s">
-        <v>16</v>
+      <c r="L7" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:12">
-      <c r="A5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6">
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="6">
         <v>4990</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5" t="s">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="6">
+        <v>806</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="6">
-        <v>803</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="8">
+      <c r="D9" s="6">
+        <v>4990</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="6">
+        <v>807</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="8">
         <v>1</v>
       </c>
-      <c r="J5" s="9"/>
+      <c r="L9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" s="11"/>
     </row>
-    <row r="6" ht="14.25" spans="1:12">
-      <c r="A6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="6">
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6">
         <v>4990</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="6">
+        <v>808</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="6">
+        <v>4990</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="8">
+        <v>813</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="8">
         <v>20</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5" t="s">
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="6">
-        <v>804</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="8">
-        <v>1</v>
-      </c>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" ht="14.25" spans="1:12">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="6">
+      <c r="D12" s="6">
         <v>4990</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="6">
-        <v>805</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="8">
-        <v>1</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" spans="1:12">
-      <c r="A8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="6">
-        <v>4990</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="6">
-        <v>806</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8">
-        <v>1</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="1:12">
-      <c r="A9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="6">
-        <v>4990</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="6">
-        <v>807</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="8">
-        <v>1</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="11"/>
-    </row>
-    <row r="10" ht="14.25" spans="1:12">
-      <c r="A10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="6">
-        <v>4990</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="6">
-        <v>808</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="8">
-        <v>1</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="1:12">
-      <c r="A11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="6">
-        <v>4990</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8">
-        <v>813</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="8">
-        <v>20</v>
-      </c>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" ht="14.25" spans="1:12">
-      <c r="A12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="6">
-        <v>4990</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>28</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="6">
+        <v>31</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="6">
         <v>520</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="12">
+      <c r="J12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="12">
         <v>1</v>
       </c>
-      <c r="J12" s="13"/>
+      <c r="L12" s="13"/>
     </row>
-    <row r="13" ht="14.25" spans="1:12">
-      <c r="A13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="6">
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="6">
         <v>4990</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>31</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="14">
+        <v>34</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="14">
         <v>522</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="14">
+      <c r="J13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="14">
         <v>1</v>
       </c>
-      <c r="J13" s="15"/>
+      <c r="L13" s="15"/>
     </row>
-    <row r="14" ht="14.25" spans="1:12">
-      <c r="A14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="6">
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="6">
         <v>4990</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="1">
+        <v>35</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="1">
         <v>524</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="14">
+      <c r="J14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:12">
-      <c r="A15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="6">
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="6">
         <v>4990</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="1">
+        <v>840</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" s="8">
+        <v>1</v>
+      </c>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="1">
-        <v>840</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="8">
-        <v>1</v>
-      </c>
-      <c r="J15" s="9"/>
-    </row>
-    <row r="16" ht="14.25" spans="1:12">
-      <c r="A16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="D16" s="6">
         <v>4990</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="1">
+        <v>37</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="1">
         <v>842</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="8">
+      <c r="J16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="8">
         <v>1</v>
       </c>
-      <c r="J16" s="9" t="s">
-        <v>22</v>
+      <c r="L16" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O13" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:Q16" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <sortState ref="A2:L63">
-    <sortCondition ref="G2"/>
+  <sortState ref="B2:N63">
+    <sortCondition ref="I2"/>
   </sortState>
-  <conditionalFormatting sqref="D2">
+  <conditionalFormatting sqref="F2">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E14:E16">
+  <conditionalFormatting sqref="G14:G16">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1 D3:D13 D17:D1048576">
+  <conditionalFormatting sqref="F1 F3:F13 F17:F1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
